--- a/05. Res/modelos/coeficientes_logit.xlsx
+++ b/05. Res/modelos/coeficientes_logit.xlsx
@@ -466,16 +466,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.6546759415951</v>
+        <v>-2.66969039693802</v>
       </c>
       <c r="C2" t="n">
-        <v>0.124075258939211</v>
+        <v>0.128007534821423</v>
       </c>
       <c r="D2" t="n">
-        <v>-21.395691327114</v>
+        <v>-20.8557285370926</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000146541301194277</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000135223194519071</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.615473056904049</v>
+        <v>0.592546800535876</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0698773357996943</v>
+        <v>0.0695776749302567</v>
       </c>
       <c r="D3" t="n">
-        <v>8.80790673915107</v>
+        <v>8.516335176906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00000000000000000127504446006611</v>
+        <v>0.0000000000000000164681757401632</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.542526230247461</v>
+        <v>0.546672160942723</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0632484983570206</v>
+        <v>0.0629084597583378</v>
       </c>
       <c r="D4" t="n">
-        <v>8.57769345265793</v>
+        <v>8.68996257487082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00000000000000000967944993272758</v>
+        <v>0.00000000000000000362558904599531</v>
       </c>
     </row>
     <row r="5">
@@ -517,16 +517,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-3.16181847329588</v>
+        <v>-3.21163169280686</v>
       </c>
       <c r="C5" t="n">
-        <v>1.00096780683662</v>
+        <v>1.00074945041021</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.15876140241538</v>
+        <v>-3.2092265366625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00158441147542476</v>
+        <v>0.00133092584313026</v>
       </c>
     </row>
     <row r="6">
@@ -534,16 +534,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.02034511033285</v>
+        <v>0.00304858892082935</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0253742217539865</v>
+        <v>0.0252816178977055</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.801802338219639</v>
+        <v>0.120585198825667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.42266730588752</v>
+        <v>0.904019592912171</v>
       </c>
     </row>
     <row r="7">
@@ -551,16 +551,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0491594098052216</v>
+        <v>0.0361967270826719</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0995128914848426</v>
+        <v>0.100402516904618</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.494000416144167</v>
+        <v>0.360516132449735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.621305885590366</v>
+        <v>0.718461194644006</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0835541604965829</v>
+        <v>-0.0109637551861888</v>
       </c>
       <c r="C8" t="n">
-        <v>0.101795758198554</v>
+        <v>0.102889898904924</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.820801986008196</v>
+        <v>-0.106558129640305</v>
       </c>
       <c r="E8" t="n">
-        <v>0.411759067175698</v>
+        <v>0.915139537096506</v>
       </c>
     </row>
     <row r="9">
@@ -585,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0222315190888174</v>
+        <v>0.0908833394503987</v>
       </c>
       <c r="C9" t="n">
-        <v>0.104664594778343</v>
+        <v>0.105652151274036</v>
       </c>
       <c r="D9" t="n">
-        <v>0.21240725324451</v>
+        <v>0.860212862250851</v>
       </c>
       <c r="E9" t="n">
-        <v>0.831789327611203</v>
+        <v>0.389671715802904</v>
       </c>
     </row>
     <row r="10">
@@ -602,16 +602,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0879353666873401</v>
+        <v>-0.0635939450011969</v>
       </c>
       <c r="C10" t="n">
-        <v>0.106757243347984</v>
+        <v>0.10781159243839</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.823694617148438</v>
+        <v>-0.589861846605577</v>
       </c>
       <c r="E10" t="n">
-        <v>0.410113098754672</v>
+        <v>0.555283274964286</v>
       </c>
     </row>
     <row r="11">
@@ -619,16 +619,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.165304791951272</v>
+        <v>-0.0943312187644472</v>
       </c>
       <c r="C11" t="n">
-        <v>0.111295598275086</v>
+        <v>0.112066355624028</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.48527699669391</v>
+        <v>-0.8417443240585</v>
       </c>
       <c r="E11" t="n">
-        <v>0.13747046284386</v>
+        <v>0.399931082272564</v>
       </c>
     </row>
     <row r="12">
@@ -636,16 +636,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.538916856672575</v>
+        <v>-0.533499164072071</v>
       </c>
       <c r="C12" t="n">
-        <v>0.130741799333984</v>
+        <v>0.134791343782467</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.12199357372998</v>
+        <v>-3.95796309392879</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000375607681366015</v>
+        <v>0.0000755916337231496</v>
       </c>
     </row>
     <row r="13">
@@ -653,16 +653,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.380544816809038</v>
+        <v>-0.447516253386771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.120348712353746</v>
+        <v>0.124271026893798</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.16201818338103</v>
+        <v>-3.6011310485848</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00156679780462166</v>
+        <v>0.000316835813202198</v>
       </c>
     </row>
     <row r="14">
@@ -670,16 +670,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.590482561464797</v>
+        <v>-0.662497178351187</v>
       </c>
       <c r="C14" t="n">
-        <v>0.119960874628749</v>
+        <v>0.124063489481068</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.92229290001597</v>
+        <v>-5.3399850441276</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00000085536063947148</v>
+        <v>0.0000000929542495631496</v>
       </c>
     </row>
     <row r="15">
@@ -687,16 +687,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.613398567016633</v>
+        <v>-0.666356597614577</v>
       </c>
       <c r="C15" t="n">
-        <v>0.122576503992083</v>
+        <v>0.126627507575869</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.00420999979123</v>
+        <v>-5.26233683637284</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000000560915836650754</v>
+        <v>0.000000142235874303407</v>
       </c>
     </row>
     <row r="16">
@@ -704,16 +704,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0285569021148663</v>
+        <v>0.0370281456893259</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0344621957403194</v>
+        <v>0.034238315068537</v>
       </c>
       <c r="D16" t="n">
-        <v>0.828644301426674</v>
+        <v>1.08148270775604</v>
       </c>
       <c r="E16" t="n">
-        <v>0.407305711837603</v>
+        <v>0.279482448643415</v>
       </c>
     </row>
     <row r="17">
@@ -721,16 +721,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0418145980531956</v>
+        <v>0.0410876210042321</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0387615040119099</v>
+        <v>0.0384656316906712</v>
       </c>
       <c r="D17" t="n">
-        <v>1.07876613973358</v>
+        <v>1.06816446782016</v>
       </c>
       <c r="E17" t="n">
-        <v>0.280691992899016</v>
+        <v>0.285446329631662</v>
       </c>
     </row>
     <row r="18">
@@ -738,16 +738,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0760820729397211</v>
+        <v>0.027078261821662</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0745116437743161</v>
+        <v>0.0741205203229421</v>
       </c>
       <c r="D18" t="n">
-        <v>1.02107629205123</v>
+        <v>0.365327465372374</v>
       </c>
       <c r="E18" t="n">
-        <v>0.307218294459965</v>
+        <v>0.714866978760113</v>
       </c>
     </row>
     <row r="19">
@@ -755,16 +755,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="n">
-        <v>0.10898214683313</v>
+        <v>0.113297289521029</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0379200250669303</v>
+        <v>0.0376050054080445</v>
       </c>
       <c r="D19" t="n">
-        <v>2.87399986262595</v>
+        <v>3.01282471021244</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00405309139354493</v>
+        <v>0.00258828373140233</v>
       </c>
     </row>
     <row r="20">
@@ -772,16 +772,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1182091567582</v>
+        <v>0.118345785028864</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0427262309744131</v>
+        <v>0.0424160858107905</v>
       </c>
       <c r="D20" t="n">
-        <v>2.766664741128</v>
+        <v>2.79011565463113</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00566329627538865</v>
+        <v>0.00526892164627917</v>
       </c>
     </row>
     <row r="21">
@@ -789,16 +789,16 @@
         <v>24</v>
       </c>
       <c r="B21" t="n">
-        <v>0.162819143401313</v>
+        <v>0.180843222482918</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0464799150162196</v>
+        <v>0.0462078154348174</v>
       </c>
       <c r="D21" t="n">
-        <v>3.50300002365529</v>
+        <v>3.91369340405244</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00046004942238128</v>
+        <v>0.0000908950342218398</v>
       </c>
     </row>
     <row r="22">
@@ -806,16 +806,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0103972198361082</v>
+        <v>0.00569123059540416</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0238922766486521</v>
+        <v>0.0237988164043481</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.435170745300019</v>
+        <v>0.239139228552743</v>
       </c>
       <c r="E22" t="n">
-        <v>0.663438495568155</v>
+        <v>0.810997624083296</v>
       </c>
     </row>
     <row r="23">
@@ -823,16 +823,16 @@
         <v>26</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.000738086793514939</v>
+        <v>-0.000757242299210803</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0000895714924405783</v>
+        <v>0.0000896738317683822</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.24019756067575</v>
+        <v>-8.44440662652487</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000000000000000171926529864595</v>
+        <v>0.0000000000000000305593716188105</v>
       </c>
     </row>
     <row r="24">
@@ -840,16 +840,16 @@
         <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0680920091094203</v>
+        <v>0.0678862462887796</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00350572417868596</v>
+        <v>0.00351910004027929</v>
       </c>
       <c r="D24" t="n">
-        <v>19.4230936716028</v>
+        <v>19.2907975083857</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000049232872208064</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000064175701315694</v>
       </c>
     </row>
     <row r="25">
@@ -857,13 +857,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n">
-        <v>2.20343826870938</v>
+        <v>2.21995987048627</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0222583273741898</v>
+        <v>0.0224301608915413</v>
       </c>
       <c r="D25" t="n">
-        <v>98.9938835774533</v>
+        <v>98.9720885739812</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -874,16 +874,16 @@
         <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0169921146277609</v>
+        <v>-0.0165109690638107</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00250444183335414</v>
+        <v>0.00249571430618254</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.78479108656469</v>
+        <v>-6.61572882076633</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0000000000116254614206304</v>
+        <v>0.0000000000369725595268542</v>
       </c>
     </row>
   </sheetData>
